--- a/archive/inside/rag_run_guide_rev1.xlsx
+++ b/archive/inside/rag_run_guide_rev1.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_노트북_연습순서" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_사내_실행순서" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_노트북_상세" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_설정_기입" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_안돌리는_파일" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_소스카테고리_수정" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_사외연습_체크리스트" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1b_노트북_연습순서" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_사내_실행순서" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_노트북_상세" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_설정_기입" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_안돌리는_파일" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_소스카테고리_수정" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66,18 +67,18 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
+      <color rgb="00185463"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
       <color rgb="005C440C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <color rgb="005C440C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00185463"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -102,12 +103,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5EAD0"/>
-        <bgColor rgb="00F5EAD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEF4F5"/>
         <bgColor rgb="00EEF4F5"/>
       </patternFill>
@@ -128,6 +123,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
         <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5EAD0"/>
+        <bgColor rgb="00F5EAD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -217,31 +218,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -252,6 +256,10 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -261,26 +269,27 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E2F0D9"/>
           <bgColor rgb="00E2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F5EAD0"/>
+          <bgColor rgb="00F5EAD0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -662,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -679,7 +688,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 · 노트북 14개 중 핵심은 6개 · 나머지는 필요할 때만 · 연노랑 = 기입</t>
+          <t>2026-09-25 · 밖(사외) 6개 → 사내 전체 · 연노랑 = 기입 · 밖에서는 설정·키 불필요</t>
         </is>
       </c>
     </row>
@@ -710,149 +719,185 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>핵심 6개</t>
+          <t>밖에서 6개</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>nb00 적재 검증 · nb12 골든셋 생성 · nb06 검색 측정 · nb10 답변 측정 · nb13 개선 비교 · nb02 청킹 품질</t>
+          <t>nb01 · nb02 · nb00 · nb03 · nb06(검색 지표) · nb10(답변 지표) — LLM 없이 전부 동작</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>선택 8개</t>
+          <t>LLM 필요 2개</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>nb01 현황 · nb03 토크나이저 · nb04 Milvus · nb05 스모크 · nb07 정형연계 · nb08 자동평가 · nb09 골든셋양식 · nb11 근거연결</t>
+          <t>nb12 골든셋 생성 · nb13 프리셋 비교 — 사내에서</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>실행 방법</t>
+          <t>나머지 6개</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Spyder 에서 파일 열고 Ctrl+Enter 로 셀 하나씩. 반드시 [0] 준비 셀부터</t>
+          <t>nb04 Milvus · nb05 스모크 · nb07 정형연계 · nb08 자동평가 · nb09 · nb11 — 필요할 때</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>결과 확인</t>
+          <t>밖에서 준비</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>콘솔 출력 + Variable Explorer 의 DataFrame. 저장물은 out/ 폴더</t>
+          <t>설정 없음. 압축 풀고 pandas · numpy · openpyxl 만 설치하면 문서 100건 · 정답지 30문항으로 바로 실행</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>기록</t>
+          <t>실행 방법</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>out/ 결과를 이력대장 · 평가팩 엑셀에 붙여넣기. 어느 시트인지는 각 시트의 "기록 위치" 열 참조</t>
+          <t>Spyder 에서 파일 열고 Ctrl+Enter 로 셀 하나씩. 반드시 [0] 준비 셀부터</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>결과 확인</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>콘솔 출력 + Variable Explorer 의 DataFrame. 저장물은 out/ 폴더</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>out/ 결과를 이력대장 · 평가팩 엑셀에 붙여넣기. 어느 시트인지는 각 시트의 "기록 위치" 열 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>순서 원칙</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>앞 단계 미달 상태에서 뒤 단계를 재면 원인을 특정할 수 없음. 1번부터 차례로</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>시트 안내</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>1_노트북_연습순서</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>개인 노트북에서 개념 잡는 순서 (샘플 데이터 100건)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>2_사내_실행순서</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>사내에서 실제로 도는 순서 · 통과 기준 · 기록 위치</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>3_노트북_상세</t>
+          <t>1_사외연습_체크리스트</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>14개 각각 무엇을 하는지 · 셀 수 · 입력 · 출력 · 필수 여부</t>
+          <t>★ 밖에서 하나씩 돌리며 확인 체크 — 무엇을 보고 무엇을 확인했는지</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>4_설정_기입</t>
+          <t>1b_노트북_연습순서</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>.env 와 lab_config 에서 채울 항목 (여기 적고 옮겨 넣기)</t>
+          <t>연습 순서 요약 (소요 시간 · LLM 필요 여부)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>5_안돌리는_파일</t>
+          <t>2_사내_실행순서</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>라이브러리 14개 역할 — 직접 실행하지 않음</t>
+          <t>사내에서 실제로 도는 순서 · 통과 기준 · 기록 위치</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>3_노트북_상세</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>14개 각각 무엇을 하는지 · 셀 수 · 입력 · 출력 · 필수 여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>4_설정_기입</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>.env 와 lab_config 에서 채울 항목 (여기 적고 옮겨 넣기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>5_안돌리는_파일</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>라이브러리 14개 역할 — 직접 실행하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>6_소스카테고리_수정</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>★ 카테고리 추가 · 제거 · 이름 변경 · 사내 코드 대응</t>
         </is>
@@ -869,29 +914,718 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>1. 사외 연습 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>밖에서 LLM 없이 하나씩 돌리며 확인 · E · F 열 기입 · 설정 · 키 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>무엇을 한다</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>확인할 것 (이게 보이면 정상)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>어디서</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>준비</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>압축 풀고 pandas · numpy · openpyxl 설치</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>[0] 준비 셀에 LAB_MODE=sample · SAMPLE_SET=100 이 찍힘</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>아무 노트북</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>준비</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>안내서 읽기</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>돌릴 노트북 6개와 순서를 안다</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>docs/practice_guide.html</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1 · 데이터</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>nb01 실행 — 소스별 분포</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>문서 100건 · 뉴스 32 · 증권사 18 … 로 나옴</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>nb01 [2] 셀</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>1 · 데이터</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>본문 길이 · 기간 확인</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2026-04 ~ 09 · 본문 중앙값 400자 내외</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>nb01 [3] 셀</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2 · 청킹</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>nb02 실행 — 정제 전후 비교</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>메일 서명 · 기사 말머리가 제거되는 것을 눈으로 확인</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>nb02 [5] 셀</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2 · 청킹</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>청크 길이 분포</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>청크 182개 · 중앙 270자 내외 · 토큰 초과율 0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>nb02 [3] 셀</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2 · 청킹</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>기준 대비 재청킹 비교</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources 의 chunk 값을 바꾸면 청크 수가 달라짐</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>nb02 [+] 셀</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>3 · 적재점검</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>nb00 실행 — 무결성 점검</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>미달 3건(청킹 누락 · 고아 청크 · 초단문)이 검출됨</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>nb00 [8] 셀</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>3 · 적재점검</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>소스 유형 매핑 확인</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>데이터의 모든 코드가 정의돼 있음 메시지</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>nb00 [1b] 셀</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>4 · 토크나이저</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>nb03 실행 — 3종 비교</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>space 보다 josa 가 hit@1 이 높게 나옴</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>nb03 [3] 셀</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>4 · 토크나이저</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>토큰 분해 눈으로 보기</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>"하이닉스의" 가 space 에서만 다른 토큰</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>nb03 [1] 셀</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>5 · 검색지표</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>nb06 실행 — 방식 6종 비교</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>bm25 R@5 0.889 · dense 0.704 처럼 값이 갈림</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>nb06 [3] 셀</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>5 · 검색지표</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>유형별 · 소스별 약점 보기</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>비교형 질문이 낮게 나오는 것 확인</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>nb06 [4] 셀</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>5 · 검색지표</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>틀린 문항 직접 보기</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>어떤 청크가 잘못 올라왔는지 원문 확인</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>nb06 [6] · [7] 셀</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>6 · 답변지표</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>nb10 실행 — 방식 2종 비교</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>모범답변(상한) vs 추출식 표가 나옴</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>nb10 [4] 셀</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>6 · 답변지표</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>합격 판정 읽기</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>충실도 · 인용은 충족 / 정확도는 미달로 나옴</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>nb10 [5] 셀</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>6 · 답변지표</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>약한 문항 확인</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>정확도 낮은 5문항의 답변을 직접 읽어봄</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>nb10 [6] 셀</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>실험 1</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>토크나이저 바꾸기</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>BM25_TOK 를 'space' → 'josa' 로 바꾸면 점수 상승</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>nb06 [2] 셀</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>실험 2</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>검색 조합 바꾸기</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>MODES 에서 모드를 빼고 더해 차이 확인</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>nb06 [3] 셀</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>실험 3</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>청크 크기 바꾸기</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources 의 chunk=500 → 300 후 nb06 재실행</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>실험 4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>RRF k · MMR λ 스윕</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>결합 · 다양성 파라미터가 점수에 주는 영향</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>nb06 [5] 셀</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>실험 5</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>정답지 직접 수정</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>질문을 바꿔 넣고 재실행 → 약한 질문 유형 파악</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>golden/golden_sample100.csv</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>사내에서 고칠 3군데 파악</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>.env · lab_config(RAW·CHUNK·MV) · lab_sources(SOURCES)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>practice_guide 6장</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>COUNTIF(B5:B27,"&lt;&gt;")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>확인 완료</t>
+        </is>
+      </c>
+      <c r="B31" s="12">
+        <f>COUNTIF(E5:E27,"확인")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>질문 있음</t>
+        </is>
+      </c>
+      <c r="B32" s="12">
+        <f>COUNTIF(E5:E27,"질문 있음")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>진행률</t>
+        </is>
+      </c>
+      <c r="B33" s="13">
+        <f>IFERROR(COUNTIF(E5:E27,"확인")/COUNTIF(B5:B27,"&lt;&gt;"),"")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E27">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"확인"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"질문 있음"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"확인,보류,질문 있음"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>1. 개인 노트북 연습 순서</t>
+          <t>1b. 연습 순서 요약</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>.env → LAB_MODE=sample · SAMPLE_SET=100 · 5~7회차면 개념 정리됨 · F · G 열 기입</t>
+          <t>밖에서 돌리는 6개 · LLM 불필요 · 나머지 8개는 사내에서</t>
         </is>
       </c>
     </row>
@@ -913,12 +1647,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>LLM 필요</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>예상 소요</t>
+          <t>소요</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -933,7 +1667,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -943,24 +1677,24 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>문서 100건이 어떻게 생겼나 — 소스별 분포 · 기간 · 본문 길이</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+          <t>데이터가 어떻게 생겼나 — 소스별 분포 · 기간 · 길이</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>불필요</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>20분</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -970,24 +1704,24 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>청크로 어떻게 쪼개지나 · 정제 전후 차이 · 노이즈 잔존</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+          <t>청크로 어떻게 쪼개지나 · 정제 전후</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>불필요</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>30분</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -997,24 +1731,24 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>적재 미달이 어떻게 표시되나 — 일부러 심어둔 결함 3종 검출</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+          <t>적재 문제를 잡아내는가 (미달 3건)</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>불필요</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>20분</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1024,24 +1758,24 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>조사 처리 방식에 따라 적중률이 달라지는 것</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+          <t>한국어 조사 처리의 영향</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>불필요</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>20분</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1051,199 +1785,114 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>★ 검색 모드 6종 점수표 — 하이브리드 · 리랭크가 무엇을 바꾸는지</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
+          <t>★ 검색 지표 — 방식 6종 비교</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>불필요</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>40분</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>nb08_auto_eval</t>
+          <t>nb10_answer_eval</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>라벨 없이 평가셋이 자동 생성되는 과정</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>있으면 좋음</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+          <t>★ 답변 지표 — 모범답변 vs 추출식</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>불필요</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>30분</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>7</v>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>nb12_golden_llm</t>
+          <t>nb12 · nb13</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>★ LLM 이 질문 · 정답 · 근거를 만드는 것 · 자가검증 6항목</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+          <t>골든셋 생성 · 프리셋 비교 — 사내에서</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>필요</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>40분</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr"/>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>8</v>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>nb10_answer_eval</t>
+          <t>nb04 · nb05 · nb07 · nb08 · nb09 · nb11</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>답변이 채점되는 방식 · 충실도 낮은 문항 직접 비교</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>필요</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>40분</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>nb13_langgraph_rag</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>★ 프리셋 v0~v6 비교표 — 보고에 쓸 결과물 형태</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>필요</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>40분</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>7 · 8 · 9 는 LLM 필요</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>.env 에 SAMPLE_MODELS=true + EMBED_MODE=api + LLM_URL · LLM_API_KEY 기입 (OpenAI 등 외부 API 가능 — 샘플 문서는 지어낸 예시)</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>건너뛰어도 되는 것</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>nb04(Milvus 없음) · nb05(체감용) · nb07(정형 연계는 나중) · nb09 · nb11(엑셀 양식 연결용)</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>확인 포인트</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>같은 질문을 검색 모드별로 돌렸을 때 순위가 어떻게 달라지는지 · 왜 그런지 청크 내용을 직접 읽어볼 것</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
+          <t>Milvus · 스모크 · 정형연계 · 자동평가 · 양식 연결</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>일부 필요</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B16:G16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B15:G15"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F13">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"완료"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"진행"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행,미착수"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1252,7 +1901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1334,7 +1983,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="14" t="n">
         <v>0</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1357,13 +2006,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1386,13 +2035,13 @@
           <t>이력대장 3_파이프라인점검</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1415,13 +2064,13 @@
           <t>이력대장 3_파이프라인점검</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1444,13 +2093,13 @@
           <t>이력대장 3_파이프라인점검</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1473,13 +2122,13 @@
           <t>이력대장 3_파이프라인점검</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1502,13 +2151,13 @@
           <t>평가팩 1b_LLM골든셋_검수</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="11" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1531,13 +2180,13 @@
           <t>평가팩 3_평가_실행기록</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1560,13 +2209,13 @@
           <t>이력대장 7_지표현황</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr"/>
-      <c r="I12" s="11" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1589,13 +2238,13 @@
           <t>이력대장 5_실험이력 · 6_프리셋비교</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="11" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1618,13 +2267,13 @@
           <t>이력대장 5_실험이력</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="11" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1647,13 +2296,13 @@
           <t>이력대장 5_실험이력</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1676,13 +2325,13 @@
           <t>평가팩 2d · 2e</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="11" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="11" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1705,13 +2354,13 @@
           <t>평가팩 스모크 시트</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="11" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1734,13 +2383,13 @@
           <t>이력대장 7_지표현황</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="11" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1763,13 +2412,13 @@
           <t>평가팩 1 · 2</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="11" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>집계</t>
         </is>
@@ -1781,7 +2430,7 @@
           <t>전체</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="12">
         <f>COUNTIF(B5:B19,"&lt;&gt;")</f>
         <v>15</v>
       </c>
@@ -1792,7 +2441,7 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="12">
         <f>COUNTIF(H5:H19,"완료")</f>
         <v>0</v>
       </c>
@@ -1803,86 +2452,86 @@
           <t>진행률</t>
         </is>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="13">
         <f>IFERROR(COUNTIF(H5:H19,"완료")/COUNTIF(B5:B19,"&lt;&gt;"),"")</f>
         <v>0.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>1~4 는 데이터 점검</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>여기서 미달이 나오면 5번 이후를 진행해도 점수 해석이 불가능</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="15" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>5 는 채점표 만들기</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>LLM 필요. 사내 LLM 엔드포인트가 없으면 nb08 자동 평가셋으로 대체</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="14" t="n"/>
-      <c r="I27" s="15" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>6 · 7 이 기준선</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>이 값이 이후 모든 비교의 원점. 설정을 바꾸기 전에 반드시 먼저 측정</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="14" t="n"/>
-      <c r="I28" s="15" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="18" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>8 부터 개선</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>회차당 설정 1개만 변경 · 같은 골든셋 고정</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-      <c r="I29" s="15" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1897,10 +2546,10 @@
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
       <formula>"진행"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
       <formula>"해당없음"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1914,7 +2563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1990,40 +2639,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>nb00_pipeline_check</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>적재 · 메타 · 청킹 · 인덱싱 무결성 점검</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>[단계별_실행도구] S00 · [P1_적재공통]</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>단계별 점검표 · 미달 항목 목록 · 소스별 분포</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>rep · fail · dist</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>이력대장 3_파이프라인점검</t>
         </is>
@@ -2040,12 +2689,12 @@
           <t>적재 현황 조사 — 소스별 분포 · 기간</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2070,40 +2719,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>nb02_parse_chunk</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>파싱 · 청킹 품질 점검</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>[P1_적재공통] S02 · S03 · S04</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>청크 길이 분포 · 노이즈 잔존 · 표 손상 · 문장 절단</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>prof · issues</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>이력대장 3_파이프라인점검</t>
         </is>
@@ -2120,12 +2769,12 @@
           <t>한국어 토크나이저 3종 비교</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2160,12 +2809,12 @@
           <t>인덱스 구성 · 건수 정합성</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2200,12 +2849,12 @@
           <t>실제 질문 20건 체감 점검</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2230,40 +2879,40 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>nb06_retrieval_eval</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>검색 지표 측정 — 모드 6종 비교</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>[P1_검색] S09~S12 · S15</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Recall@k · MRR · nDCG 모드별 표 · 유형별 분해</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>summary · detail</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>평가팩 3_평가_실행기록</t>
         </is>
@@ -2280,12 +2929,12 @@
           <t>정형 데이터 연계 — 라우팅 · SQL · 검증</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2320,12 +2969,12 @@
           <t>라벨 없는 평가셋 자동 생성 · 측정</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="14" t="n">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2350,80 +2999,80 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>nb09_golden_build</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>골든셋 구성 → 평가 실행 (엑셀 연계)</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>체크리스트 없음 — 평가팩 엑셀 연계</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>검수 시트 · 확정 골든셋 · 실행 기록 양식</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>review · runrec</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>평가팩 1 · 2 · 3</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>nb10_answer_eval</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>답변 품질 측정 — RAGAS 계열 지표</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>[P1_검색] S14 · S15</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>충실도 · 적합도 · 정확도 · 인용 · 거절 + 합격 판정</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>auto · summary</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>이력대장 7_지표현황</t>
         </is>
@@ -2440,12 +3089,12 @@
           <t>질문에 근거 문서 연결 · 수집 공백 분리</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="14" t="n">
         <v>6</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2470,80 +3119,80 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>nb12_golden_llm</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>LLM 으로 골든셋 생성 · 자가검증 · 검수</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>[P1_검색] S15</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>질문 · 정답 · 근거 + 자가검증 6항목 + 검수 시트</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>gen · chk · gold</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>평가팩 1b_LLM골든셋_검수</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>nb13_langgraph_rag</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>노드 구성별 비교 — 개선 정량화</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>핵심</t>
         </is>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>[P1_검색] S08 · S11 · S12 · S14</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>프리셋 v0~v6 지표 비교 · 증감 · 퇴행 문항</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>summ · dlt · detail</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>이력대장 5 · 6</t>
         </is>
@@ -2559,7 +3208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2623,7 +3272,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2643,11 +3292,11 @@
           <t>sample → live</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr"/>
-      <c r="F5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2667,11 +3316,11 @@
           <t>16 또는 100</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2691,11 +3340,11 @@
           <t>true / false</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2715,11 +3364,11 @@
           <t>host:1521/SERVICE</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2739,11 +3388,11 @@
           <t>http://host:19530</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2763,11 +3412,11 @@
           <t>local / api</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2787,11 +3436,11 @@
           <t>local / api / none</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr"/>
-      <c r="F11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
@@ -2811,11 +3460,11 @@
           <t>.../v1/chat/completions</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>lab_config</t>
         </is>
@@ -2835,11 +3484,11 @@
           <t>RAG_RAW_DOC</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>lab_config</t>
         </is>
@@ -2859,11 +3508,11 @@
           <t>위 이름 그대로</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>lab_config</t>
         </is>
@@ -2883,11 +3532,11 @@
           <t>RAG_CHUNK</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>lab_config</t>
         </is>
@@ -2907,11 +3556,11 @@
           <t>위 이름 그대로</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>lab_config</t>
         </is>
@@ -2931,11 +3580,11 @@
           <t>없으면 None</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr"/>
-      <c r="F17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>lab_config</t>
         </is>
@@ -2955,11 +3604,11 @@
           <t>NEWS · BROKER · INSTITUTION · EMAIL · MEETING · REPORT · EXEC_REPORT</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>lab_config</t>
         </is>
@@ -2979,24 +3628,24 @@
           <t>8192</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
-      <c r="F19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>주의</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>비밀번호 · API 키는 이 표에 적지 않는다. .env 에만 직접 입력하고 파일은 공유하지 않는다.</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="15" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3014,7 +3663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3060,17 +3709,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>lab_config.py</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>설정 단일 지점 — 접속 정보 · 테이블 · 컬럼 매핑 · 실행 모드</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>★ 수정함</t>
         </is>
@@ -3087,7 +3736,7 @@
           <t>Oracle 읽기 / 샘플 제공 / 결과 저장</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>안 열어도 됨</t>
         </is>
@@ -3104,7 +3753,7 @@
           <t>소스별 정제 · 토큰 수 · 품질 지표 · 근사 중복</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>안 열어도 됨</t>
         </is>
@@ -3121,7 +3770,7 @@
           <t>BM25 · 임베딩 · 리랭커 · Milvus · RRF · MMR · LLM 답변</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>안 열어도 됨</t>
         </is>
@@ -3138,7 +3787,7 @@
           <t>적재 무결성 점검 기준(CRITERIA) · 소스별 필수 메타</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>기준 조정 시</t>
         </is>
@@ -3155,7 +3804,7 @@
           <t>검색 지표 계산 — Hit · Recall · MRR · nDCG</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>안 열어도 됨</t>
         </is>
@@ -3172,7 +3821,7 @@
           <t>표준 지표 16종 정의 · 계산 · LLM 채점 프롬프트</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>기준 조정 시</t>
         </is>
@@ -3189,7 +3838,7 @@
           <t>라벨 없는 평가셋 생성 · 근거 문서 연결</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>안 열어도 됨</t>
         </is>
@@ -3206,7 +3855,7 @@
           <t>LLM 골든셋 생성 · 자가검증 · 유형 배분</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>프롬프트 조정 시</t>
         </is>
@@ -3223,7 +3872,7 @@
           <t>LangGraph 노드 · 프리셋 v0~v6 · 비교</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>프리셋 추가 시</t>
         </is>
@@ -3240,7 +3889,7 @@
           <t>정형 연계 — 라우팅 · SQL 생성 · 정적 검증 · 실행</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>허용목록 조정 시</t>
         </is>
@@ -3257,7 +3906,7 @@
           <t>샘플 데이터 16건 (sample 모드 기본)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>안 열어도 됨</t>
         </is>
@@ -3274,24 +3923,24 @@
           <t>확장 샘플 100건 (SAMPLE_SET=100)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>안 열어도 됨</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>lab_sources.py</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>★ 소스 카테고리 정의 — 코드 · 이름 · 사내 DB 값 · 필수 메타 · 정제 · 청킹</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>★ 수정함</t>
         </is>
@@ -3307,7 +3956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3558,46 +4207,46 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>원칙</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>카테고리에 관한 모든 것이 SOURCES 한 곳에 있다. lab_config 는 접속 · 테이블 설정만 담당한다.</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="15" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>반드시 확인</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>nb00 [1b] — 정의에 없는 코드는 필수 메타 · 정제 규칙이 적용되지 않은 채 통과한다.</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>수정 후</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Spyder 에서 [0] 준비 셀을 다시 실행해야 반영된다.</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
